--- a/Assets/Data/Animations.xlsx
+++ b/Assets/Data/Animations.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
   <si>
     <t>Id</t>
   </si>
@@ -73,6 +73,9 @@
     <t>NA_Effekseer/NA_Fire_001</t>
   </si>
   <si>
+    <t>FireOne1</t>
+  </si>
+  <si>
     <t>炎攻撃</t>
   </si>
   <si>
@@ -88,7 +91,7 @@
     <t>NA_Effekseer/NA_magic_004_c1</t>
   </si>
   <si>
-    <t>NA_Effekseer_Vol_2/NA_v2_2.5d_element reservoir_fire</t>
+    <t>FireAll2</t>
   </si>
   <si>
     <t>雷攻撃</t>
@@ -124,7 +127,7 @@
     <t>NA_Effekseer_Vol_2/NA_v2_2.5d_jump move_normal</t>
   </si>
   <si>
-    <t>NA_Effekseer/NA_slash_003_c3</t>
+    <t>IceOne1</t>
   </si>
   <si>
     <t>氷攻撃</t>
@@ -291,45 +294,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -351,14 +324,67 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -373,15 +399,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -390,21 +431,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -419,33 +445,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -458,7 +461,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,13 +509,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,13 +533,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,37 +575,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,19 +605,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,55 +617,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,7 +641,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,17 +655,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -682,15 +681,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -702,6 +692,30 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -724,8 +738,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -738,17 +752,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -757,145 +760,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1512,7 +1515,7 @@
         <v>101</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1533,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1567,7 +1570,7 @@
         <v>103</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1593,7 +1596,7 @@
         <v>104</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1619,7 +1622,7 @@
         <v>111</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1645,7 +1648,7 @@
         <v>112</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1671,7 +1674,7 @@
         <v>113</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1697,7 +1700,7 @@
         <v>114</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1723,7 +1726,7 @@
         <v>121</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1770,7 +1773,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1778,7 +1781,7 @@
         <v>202</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1804,7 +1807,7 @@
         <v>203</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1830,7 +1833,7 @@
         <v>204</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1856,7 +1859,7 @@
         <v>205</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1882,7 +1885,7 @@
         <v>211</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1908,7 +1911,7 @@
         <v>212</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1934,7 +1937,7 @@
         <v>213</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1960,7 +1963,7 @@
         <v>214</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1986,7 +1989,7 @@
         <v>221</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -2012,7 +2015,7 @@
         <v>222</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -2038,7 +2041,7 @@
         <v>301</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -2059,7 +2062,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2067,7 +2070,7 @@
         <v>302</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -2093,7 +2096,7 @@
         <v>303</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -2119,7 +2122,7 @@
         <v>304</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -2145,7 +2148,7 @@
         <v>305</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -2171,7 +2174,7 @@
         <v>311</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -2197,7 +2200,7 @@
         <v>312</v>
       </c>
       <c r="B36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2223,7 +2226,7 @@
         <v>313</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -2249,7 +2252,7 @@
         <v>314</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -2275,7 +2278,7 @@
         <v>321</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -2301,7 +2304,7 @@
         <v>322</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -2327,7 +2330,7 @@
         <v>401</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2348,7 +2351,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -2356,7 +2359,7 @@
         <v>402</v>
       </c>
       <c r="B42" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2408,7 +2411,7 @@
         <v>404</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -2434,7 +2437,7 @@
         <v>405</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -2460,7 +2463,7 @@
         <v>411</v>
       </c>
       <c r="B46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -2486,7 +2489,7 @@
         <v>412</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -2512,7 +2515,7 @@
         <v>413</v>
       </c>
       <c r="B48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -2538,7 +2541,7 @@
         <v>414</v>
       </c>
       <c r="B49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -2564,7 +2567,7 @@
         <v>421</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -2590,7 +2593,7 @@
         <v>422</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -2616,7 +2619,7 @@
         <v>501</v>
       </c>
       <c r="B52" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -2637,7 +2640,7 @@
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2645,7 +2648,7 @@
         <v>502</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -2671,7 +2674,7 @@
         <v>503</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -2697,7 +2700,7 @@
         <v>504</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -2723,7 +2726,7 @@
         <v>505</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -2749,7 +2752,7 @@
         <v>511</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -2775,7 +2778,7 @@
         <v>512</v>
       </c>
       <c r="B58" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -2801,7 +2804,7 @@
         <v>513</v>
       </c>
       <c r="B59" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -2827,7 +2830,7 @@
         <v>514</v>
       </c>
       <c r="B60" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -2853,7 +2856,7 @@
         <v>521</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -2879,7 +2882,7 @@
         <v>522</v>
       </c>
       <c r="B62" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -2905,7 +2908,7 @@
         <v>601</v>
       </c>
       <c r="B63" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -2931,7 +2934,7 @@
         <v>1001</v>
       </c>
       <c r="B64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -2957,7 +2960,7 @@
         <v>1002</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -2983,7 +2986,7 @@
         <v>1003</v>
       </c>
       <c r="B66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3009,7 +3012,7 @@
         <v>1004</v>
       </c>
       <c r="B67" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -3035,7 +3038,7 @@
         <v>1005</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -3061,7 +3064,7 @@
         <v>2001</v>
       </c>
       <c r="B69" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -3087,7 +3090,7 @@
         <v>2002</v>
       </c>
       <c r="B70" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -3113,7 +3116,7 @@
         <v>2003</v>
       </c>
       <c r="B71" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -3139,7 +3142,7 @@
         <v>2004</v>
       </c>
       <c r="B72" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -3165,7 +3168,7 @@
         <v>2005</v>
       </c>
       <c r="B73" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -3191,7 +3194,7 @@
         <v>2006</v>
       </c>
       <c r="B74" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -3217,7 +3220,7 @@
         <v>5001</v>
       </c>
       <c r="B75" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -3243,7 +3246,7 @@
         <v>5002</v>
       </c>
       <c r="B76" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3269,7 +3272,7 @@
         <v>5003</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -3295,7 +3298,7 @@
         <v>5004</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3321,7 +3324,7 @@
         <v>5005</v>
       </c>
       <c r="B79" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -3347,7 +3350,7 @@
         <v>5006</v>
       </c>
       <c r="B80" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -3373,7 +3376,7 @@
         <v>5007</v>
       </c>
       <c r="B81" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -3399,7 +3402,7 @@
         <v>5008</v>
       </c>
       <c r="B82" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -3425,7 +3428,7 @@
         <v>5009</v>
       </c>
       <c r="B83" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C83">
         <v>0</v>

--- a/Assets/Data/Animations.xlsx
+++ b/Assets/Data/Animations.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="147">
   <si>
     <t>Id</t>
   </si>
@@ -46,202 +46,370 @@
     <t>tktk01/Magic2</t>
   </si>
   <si>
-    <t>NA_Effekseer/NA_healing_001</t>
+    <t>NA_Effekseer/NA_shooting_002</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_aura_001</t>
+  </si>
+  <si>
+    <t>バフ</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_aura_002</t>
+  </si>
+  <si>
+    <t>デバフ</t>
+  </si>
+  <si>
+    <t>tktk01/Fire2</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_Fire_001</t>
+  </si>
+  <si>
+    <t>FireOne1</t>
+  </si>
+  <si>
+    <t>炎攻撃</t>
+  </si>
+  <si>
+    <t>FireOne2</t>
+  </si>
+  <si>
+    <t>FireAll1</t>
+  </si>
+  <si>
+    <t>FireAll2</t>
+  </si>
+  <si>
+    <t>FireAll3</t>
+  </si>
+  <si>
+    <t>ThunderOne1</t>
+  </si>
+  <si>
+    <t>雷攻撃</t>
+  </si>
+  <si>
+    <t>ThunderOne2</t>
+  </si>
+  <si>
+    <t>ThunderAll1</t>
+  </si>
+  <si>
+    <t>ThunderAll2</t>
+  </si>
+  <si>
+    <t>ThunderAll3</t>
+  </si>
+  <si>
+    <t>IceOne1</t>
+  </si>
+  <si>
+    <t>氷攻撃</t>
+  </si>
+  <si>
+    <t>IceOne2</t>
+  </si>
+  <si>
+    <t>IceAll1</t>
+  </si>
+  <si>
+    <t>IceAll2</t>
+  </si>
+  <si>
+    <t>IceAll3</t>
+  </si>
+  <si>
+    <t>LightOne1</t>
+  </si>
+  <si>
+    <t>光攻撃</t>
+  </si>
+  <si>
+    <t>LightOne2</t>
+  </si>
+  <si>
+    <t>LightAll1</t>
+  </si>
+  <si>
+    <t>LightAll2</t>
+  </si>
+  <si>
+    <t>LightAll3</t>
+  </si>
+  <si>
+    <t>DarknessOne1</t>
+  </si>
+  <si>
+    <t>闇攻撃</t>
+  </si>
+  <si>
+    <t>DarknessOne2</t>
+  </si>
+  <si>
+    <t>DarknessAll1</t>
+  </si>
+  <si>
+    <t>DarknessAll2</t>
+  </si>
+  <si>
+    <t>DarknessAll3</t>
+  </si>
+  <si>
+    <t>NeutralOne1</t>
+  </si>
+  <si>
+    <t>NeutralOne2</t>
+  </si>
+  <si>
+    <t>NeutralAll1</t>
+  </si>
+  <si>
+    <t>NeutralAll2</t>
+  </si>
+  <si>
+    <t>NeutralAll3</t>
+  </si>
+  <si>
+    <t>HealOne1</t>
   </si>
   <si>
     <t>回復</t>
   </si>
   <si>
-    <t>NA_Effekseer/NA_shooting_002</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_aura_001</t>
-  </si>
-  <si>
-    <t>バフ</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_aura_002</t>
-  </si>
-  <si>
-    <t>デバフ</t>
-  </si>
-  <si>
-    <t>tktk01/Fire2</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_Fire_001</t>
-  </si>
-  <si>
-    <t>FireOne1</t>
-  </si>
-  <si>
-    <t>炎攻撃</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_aura_003_c1</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_sword_001</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_magic_006_c1</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_magic_004_c1</t>
-  </si>
-  <si>
-    <t>FireAll2</t>
-  </si>
-  <si>
-    <t>雷攻撃</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_net_001</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_status_005</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_magic_003</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_exchange_001</t>
-  </si>
-  <si>
-    <t>tktk01/Blow10</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_net_002</t>
-  </si>
-  <si>
-    <t>EffekseerVol_3/NA_v3_3d_element shot_electric</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_aura_003</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_magic_006_c5</t>
-  </si>
-  <si>
-    <t>NA_Effekseer_Vol_2/NA_v2_2.5d_jump move_normal</t>
-  </si>
-  <si>
-    <t>IceOne1</t>
-  </si>
-  <si>
-    <t>氷攻撃</t>
-  </si>
-  <si>
-    <t>tktk02/Light1</t>
-  </si>
-  <si>
-    <t>tktk02/Gun2</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_wave_001</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_magic_006</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_barrier_001</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_magic_008_c3</t>
-  </si>
-  <si>
-    <t>EffekseerVol_3/NA_v3_3d_fairy light_1</t>
-  </si>
-  <si>
-    <t>EffekseerVol_3/NA_v3_2.5d_fog_2</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_magic_006_c2</t>
-  </si>
-  <si>
-    <t>EffekseerVol_3/NA_v3_3d_residue_water</t>
-  </si>
-  <si>
-    <t>光攻撃</t>
-  </si>
-  <si>
-    <t>tktk01/Sword7</t>
-  </si>
-  <si>
-    <t>tktk01/Light2</t>
-  </si>
-  <si>
-    <t>tktk02/Light3</t>
-  </si>
-  <si>
-    <t>tktk01/Cure2</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_aura_005</t>
-  </si>
-  <si>
-    <t>EffekseerVol_3/NA_v3_2.5d_crash_1</t>
-  </si>
-  <si>
-    <t>EffekseerVol_3/NA_v3_2.5d_shining_5</t>
-  </si>
-  <si>
-    <t>tktk01/Cure1</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_magic_006_c7</t>
-  </si>
-  <si>
-    <t>tktk02/Dark1</t>
-  </si>
-  <si>
-    <t>闇攻撃</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_wave_003</t>
-  </si>
-  <si>
-    <t>tktk01/Dark3</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_magic_002</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_curse_001</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_smoke_003_c7</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_magic_009</t>
-  </si>
-  <si>
-    <t>MakerEffect/Death</t>
-  </si>
-  <si>
-    <t>MakerEffect/Darkness1</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_magic_006_c8</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_smoke_004</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_cut-in_002_1</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_cut-in_002_2</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_cut-in_002_3</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_cut-in_002_4</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_cut-in_002_5</t>
+    <t>HealOne2</t>
+  </si>
+  <si>
+    <t>HealAll1</t>
+  </si>
+  <si>
+    <t>HealAll2</t>
+  </si>
+  <si>
+    <t>CureOne1</t>
+  </si>
+  <si>
+    <t>CureOne2</t>
+  </si>
+  <si>
+    <t>CureAll1</t>
+  </si>
+  <si>
+    <t>CureAll2</t>
+  </si>
+  <si>
+    <t>Revive1</t>
+  </si>
+  <si>
+    <t>Revive2</t>
+  </si>
+  <si>
+    <t>Powerup1</t>
+  </si>
+  <si>
+    <t>Powerup2</t>
+  </si>
+  <si>
+    <t>Powerup3</t>
+  </si>
+  <si>
+    <t>Powerdown1</t>
+  </si>
+  <si>
+    <t>Powerdown2</t>
+  </si>
+  <si>
+    <t>Powerdown3</t>
+  </si>
+  <si>
+    <t>Bind</t>
+  </si>
+  <si>
+    <t>Absorb</t>
+  </si>
+  <si>
+    <t>Poison</t>
+  </si>
+  <si>
+    <t>Blind</t>
+  </si>
+  <si>
+    <t>Silence</t>
+  </si>
+  <si>
+    <t>Sleep</t>
+  </si>
+  <si>
+    <t>Confusion</t>
+  </si>
+  <si>
+    <t>Paralyze</t>
+  </si>
+  <si>
+    <t>Death</t>
+  </si>
+  <si>
+    <t>HitPhysical</t>
+  </si>
+  <si>
+    <t>HitEffect</t>
+  </si>
+  <si>
+    <t>HitFire</t>
+  </si>
+  <si>
+    <t>HitIce</t>
+  </si>
+  <si>
+    <t>HitThunder</t>
+  </si>
+  <si>
+    <t>SlashPhysical</t>
+  </si>
+  <si>
+    <t>SlashEffect</t>
+  </si>
+  <si>
+    <t>SlashFire</t>
+  </si>
+  <si>
+    <t>SlashIce</t>
+  </si>
+  <si>
+    <t>SlashThunder</t>
+  </si>
+  <si>
+    <t>PiercePhysical</t>
+  </si>
+  <si>
+    <t>PierceEffect</t>
+  </si>
+  <si>
+    <t>PierceFire</t>
+  </si>
+  <si>
+    <t>PierceIce</t>
+  </si>
+  <si>
+    <t>PierceThunder</t>
+  </si>
+  <si>
+    <t>ClawPhysical</t>
+  </si>
+  <si>
+    <t>ClawEffect</t>
+  </si>
+  <si>
+    <t>ClawFire</t>
+  </si>
+  <si>
+    <t>ClawIce</t>
+  </si>
+  <si>
+    <t>ClawThunder</t>
+  </si>
+  <si>
+    <t>HitSpecial1</t>
+  </si>
+  <si>
+    <t>HitSpecial2</t>
+  </si>
+  <si>
+    <t>SlashSpecial1</t>
+  </si>
+  <si>
+    <t>SlashSpecial2</t>
+  </si>
+  <si>
+    <t>PierceSpecial1</t>
+  </si>
+  <si>
+    <t>PierceSpecial2</t>
+  </si>
+  <si>
+    <t>ClawSpecial</t>
+  </si>
+  <si>
+    <t>ArrowSpecial</t>
+  </si>
+  <si>
+    <t>GeneralSpecial1</t>
+  </si>
+  <si>
+    <t>GeneralSpecial2</t>
+  </si>
+  <si>
+    <t>Breath</t>
+  </si>
+  <si>
+    <t>Pollen</t>
+  </si>
+  <si>
+    <t>SonicWave</t>
+  </si>
+  <si>
+    <t>Fog</t>
+  </si>
+  <si>
+    <t>Song</t>
+  </si>
+  <si>
+    <t>Shout</t>
+  </si>
+  <si>
+    <t>Sweep</t>
+  </si>
+  <si>
+    <t>Bodyslam</t>
+  </si>
+  <si>
+    <t>Flash</t>
+  </si>
+  <si>
+    <t>WaterOne1</t>
+  </si>
+  <si>
+    <t>WaterOne2</t>
+  </si>
+  <si>
+    <t>WaterAll1</t>
+  </si>
+  <si>
+    <t>WaterAll2</t>
+  </si>
+  <si>
+    <t>WaterAll3</t>
+  </si>
+  <si>
+    <t>EarthOne1</t>
+  </si>
+  <si>
+    <t>EarthOne2</t>
+  </si>
+  <si>
+    <t>EarthAll1</t>
+  </si>
+  <si>
+    <t>EarthAll2</t>
+  </si>
+  <si>
+    <t>EarthAll3</t>
+  </si>
+  <si>
+    <t>WindOne1</t>
+  </si>
+  <si>
+    <t>WindOne2</t>
+  </si>
+  <si>
+    <t>WindAll1</t>
+  </si>
+  <si>
+    <t>WindAll2</t>
+  </si>
+  <si>
+    <t>WindAll3</t>
   </si>
   <si>
     <t>NA_Effekseer_Vol_2/NA_v2_3d_Magic Circle_normal</t>
@@ -294,9 +462,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -308,9 +476,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,37 +513,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -369,44 +551,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -429,6 +574,14 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -445,10 +598,25 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -461,19 +629,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -485,31 +671,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -521,37 +695,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -569,13 +725,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,19 +749,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,19 +779,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -635,13 +809,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -655,13 +823,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -677,21 +849,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -720,6 +877,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -739,16 +905,18 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -760,145 +928,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1257,7 +1425,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I132"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="51.1818181818182" customWidth="1"/>
@@ -1313,7 +1481,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -1339,15 +1507,15 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:8">
       <c r="A4">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -1359,50 +1527,50 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
-      <c r="I4" t="s">
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>51</v>
+      </c>
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0.5</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>60</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
         <v>12</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>42</v>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -1420,7 +1588,7 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -1429,9 +1597,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:8">
       <c r="A7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -1443,76 +1611,76 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>60</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>101</v>
+      </c>
+      <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>42</v>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9">
-        <v>63</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0.35</v>
+      </c>
+      <c r="F9">
+        <v>1.2</v>
+      </c>
+      <c r="G9">
+        <v>60</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
         <v>18</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>42</v>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
@@ -1524,27 +1692,24 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G10">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1553,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G11">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -1567,7 +1732,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
@@ -1579,13 +1744,13 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G12">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -1593,7 +1758,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
@@ -1605,21 +1770,21 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G13">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:9">
       <c r="A14">
-        <v>111</v>
+        <v>201</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
@@ -1631,24 +1796,27 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G14">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
+      </c>
+      <c r="I14" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
-        <v>112</v>
+        <v>202</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1657,13 +1825,13 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G15">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1671,10 +1839,10 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>113</v>
+        <v>211</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1683,13 +1851,13 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G16">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1697,10 +1865,10 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>114</v>
+        <v>212</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1709,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G17">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1723,10 +1891,10 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>121</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1735,13 +1903,13 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G18">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -1749,10 +1917,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19">
-        <v>201</v>
+        <v>301</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1761,27 +1929,27 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="F19">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G19">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>202</v>
+        <v>302</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1790,13 +1958,13 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G20">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1804,10 +1972,10 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>203</v>
+        <v>311</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1816,13 +1984,13 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G21">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1830,10 +1998,10 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>204</v>
+        <v>312</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1842,13 +2010,13 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G22">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1856,10 +2024,10 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>205</v>
+        <v>313</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1868,24 +2036,24 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G23">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:9">
       <c r="A24">
-        <v>211</v>
+        <v>401</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1894,24 +2062,27 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G24">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
+      </c>
+      <c r="I24" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>212</v>
+        <v>402</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1920,13 +2091,13 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G25">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1934,10 +2105,10 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>213</v>
+        <v>411</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1946,13 +2117,13 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G26">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -1960,10 +2131,10 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>214</v>
+        <v>412</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1972,13 +2143,13 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G27">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -1986,10 +2157,10 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>221</v>
+        <v>413</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1998,50 +2169,53 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G28">
+        <v>60</v>
+      </c>
+      <c r="H28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29">
+        <v>501</v>
+      </c>
+      <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0.25</v>
+      </c>
+      <c r="F29">
+        <v>1.2</v>
+      </c>
+      <c r="G29">
+        <v>60</v>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" t="s">
         <v>42</v>
       </c>
-      <c r="H28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29">
-        <v>222</v>
-      </c>
-      <c r="B29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29">
-        <v>42</v>
-      </c>
-      <c r="H29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30">
-        <v>301</v>
+        <v>502</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -2050,27 +2224,24 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F30">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G30">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
-      </c>
-      <c r="I30" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>302</v>
+        <v>511</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -2079,13 +2250,13 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G31">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -2093,10 +2264,10 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>303</v>
+        <v>512</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -2105,13 +2276,13 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G32">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -2119,25 +2290,25 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>304</v>
+        <v>513</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G33">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -2145,10 +2316,10 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>305</v>
+        <v>601</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -2157,13 +2328,13 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G34">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -2171,10 +2342,10 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>311</v>
+        <v>602</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -2183,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G35">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -2197,10 +2368,10 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>312</v>
+        <v>611</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2209,13 +2380,13 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G36">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -2223,10 +2394,10 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>313</v>
+        <v>612</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -2235,13 +2406,13 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G37">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -2249,36 +2420,36 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>314</v>
+        <v>613</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G38">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:9">
       <c r="A39">
-        <v>321</v>
+        <v>701</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -2287,24 +2458,27 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G39">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:8">
+      <c r="I39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40">
-        <v>322</v>
+        <v>702</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -2313,24 +2487,27 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G40">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41">
-        <v>401</v>
+        <v>711</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2339,27 +2516,27 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="F41">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G41">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42">
-        <v>402</v>
+        <v>712</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2368,24 +2545,27 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G42">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:8">
+      <c r="I42" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43">
-        <v>403</v>
+        <v>721</v>
       </c>
       <c r="B43" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -2394,24 +2574,27 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G43">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:8">
+      <c r="I43" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44">
-        <v>404</v>
+        <v>722</v>
       </c>
       <c r="B44" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -2420,24 +2603,27 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G44">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:8">
+      <c r="I44" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45">
-        <v>405</v>
+        <v>731</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -2446,50 +2632,56 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G45">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:8">
+      <c r="I45" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46">
-        <v>411</v>
+        <v>732</v>
       </c>
       <c r="B46" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0.5</v>
+      </c>
+      <c r="F46">
+        <v>1.2</v>
+      </c>
+      <c r="G46">
+        <v>60</v>
+      </c>
+      <c r="H46" t="b">
+        <v>1</v>
+      </c>
+      <c r="I46" t="s">
         <v>53</v>
       </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-      <c r="E46">
-        <v>1</v>
-      </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-      <c r="G46">
-        <v>42</v>
-      </c>
-      <c r="H46" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47">
-        <v>412</v>
+        <v>741</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -2498,24 +2690,27 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G47">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:8">
+      <c r="I47" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48">
-        <v>413</v>
+        <v>742</v>
       </c>
       <c r="B48" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -2524,24 +2719,27 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G48">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
+      </c>
+      <c r="I48" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>414</v>
+        <v>801</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -2550,13 +2748,13 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G49">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2564,10 +2762,10 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
-        <v>421</v>
+        <v>802</v>
       </c>
       <c r="B50" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -2576,13 +2774,13 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G50">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -2590,10 +2788,10 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51">
-        <v>422</v>
+        <v>803</v>
       </c>
       <c r="B51" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -2602,24 +2800,24 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G51">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:8">
       <c r="A52">
-        <v>501</v>
+        <v>811</v>
       </c>
       <c r="B52" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -2628,27 +2826,24 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="F52">
         <v>1.2</v>
       </c>
       <c r="G52">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
-      </c>
-      <c r="I52" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53">
-        <v>502</v>
+        <v>812</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -2657,13 +2852,13 @@
         <v>0</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G53">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -2671,10 +2866,10 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54">
-        <v>503</v>
+        <v>813</v>
       </c>
       <c r="B54" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -2683,13 +2878,13 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G54">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -2697,10 +2892,10 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>504</v>
+        <v>901</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -2709,13 +2904,13 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G55">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -2723,10 +2918,10 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>505</v>
+        <v>902</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -2735,13 +2930,13 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G56">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -2749,10 +2944,10 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>511</v>
+        <v>903</v>
       </c>
       <c r="B57" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -2761,13 +2956,13 @@
         <v>0</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G57">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -2775,10 +2970,10 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>512</v>
+        <v>904</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -2787,13 +2982,13 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G58">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -2801,25 +2996,25 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>513</v>
+        <v>905</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G59">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -2827,25 +3022,25 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>514</v>
+        <v>906</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G60">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -2853,10 +3048,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>521</v>
+        <v>907</v>
       </c>
       <c r="B61" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -2865,13 +3060,13 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G61">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -2879,10 +3074,10 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>522</v>
+        <v>908</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -2891,13 +3086,13 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G62">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -2905,10 +3100,10 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>601</v>
+        <v>909</v>
       </c>
       <c r="B63" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -2917,13 +3112,13 @@
         <v>0</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G63">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -2934,7 +3129,7 @@
         <v>1001</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -2943,13 +3138,13 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G64">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -2960,7 +3155,7 @@
         <v>1002</v>
       </c>
       <c r="B65" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -2969,13 +3164,13 @@
         <v>0</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G65">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -2986,7 +3181,7 @@
         <v>1003</v>
       </c>
       <c r="B66" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -2995,13 +3190,13 @@
         <v>0</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G66">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -3012,7 +3207,7 @@
         <v>1004</v>
       </c>
       <c r="B67" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -3021,13 +3216,13 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G67">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -3038,7 +3233,7 @@
         <v>1005</v>
       </c>
       <c r="B68" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -3047,13 +3242,13 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G68">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -3061,10 +3256,10 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>2001</v>
+        <v>1011</v>
       </c>
       <c r="B69" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -3073,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G69">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -3087,10 +3282,10 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>2002</v>
+        <v>1012</v>
       </c>
       <c r="B70" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -3099,13 +3294,13 @@
         <v>0</v>
       </c>
       <c r="E70">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G70">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -3113,10 +3308,10 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>2003</v>
+        <v>1013</v>
       </c>
       <c r="B71" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -3125,13 +3320,13 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G71">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3139,10 +3334,10 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72">
-        <v>2004</v>
+        <v>1014</v>
       </c>
       <c r="B72" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -3151,13 +3346,13 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G72">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -3165,10 +3360,10 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
-        <v>2005</v>
+        <v>1015</v>
       </c>
       <c r="B73" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -3177,13 +3372,13 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G73">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -3191,10 +3386,10 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74">
-        <v>2006</v>
+        <v>1021</v>
       </c>
       <c r="B74" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -3203,13 +3398,13 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G74">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -3217,10 +3412,10 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
-        <v>5001</v>
+        <v>1022</v>
       </c>
       <c r="B75" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -3229,13 +3424,13 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G75">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -3243,10 +3438,10 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>5002</v>
+        <v>1023</v>
       </c>
       <c r="B76" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3255,13 +3450,13 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G76">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -3269,10 +3464,10 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
-        <v>5003</v>
+        <v>1024</v>
       </c>
       <c r="B77" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -3281,13 +3476,13 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G77">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -3295,10 +3490,10 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78">
-        <v>5004</v>
+        <v>1025</v>
       </c>
       <c r="B78" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3307,13 +3502,13 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G78">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -3321,10 +3516,10 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79">
-        <v>5005</v>
+        <v>1031</v>
       </c>
       <c r="B79" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -3333,13 +3528,13 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G79">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -3347,10 +3542,10 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80">
-        <v>5006</v>
+        <v>1032</v>
       </c>
       <c r="B80" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -3359,13 +3554,13 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G80">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -3373,10 +3568,10 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81">
-        <v>5007</v>
+        <v>1033</v>
       </c>
       <c r="B81" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -3385,13 +3580,13 @@
         <v>0</v>
       </c>
       <c r="E81">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G81">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -3399,10 +3594,10 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82">
-        <v>5008</v>
+        <v>1034</v>
       </c>
       <c r="B82" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -3411,13 +3606,13 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G82">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -3425,27 +3620,1301 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83">
+        <v>1035</v>
+      </c>
+      <c r="B83" t="s">
+        <v>97</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>0.35</v>
+      </c>
+      <c r="F83">
+        <v>1.2</v>
+      </c>
+      <c r="G83">
+        <v>60</v>
+      </c>
+      <c r="H83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84">
+        <v>1041</v>
+      </c>
+      <c r="B84" t="s">
+        <v>98</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0.35</v>
+      </c>
+      <c r="F84">
+        <v>1.2</v>
+      </c>
+      <c r="G84">
+        <v>60</v>
+      </c>
+      <c r="H84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85">
+        <v>1042</v>
+      </c>
+      <c r="B85" t="s">
+        <v>99</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0.35</v>
+      </c>
+      <c r="F85">
+        <v>1.2</v>
+      </c>
+      <c r="G85">
+        <v>60</v>
+      </c>
+      <c r="H85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86">
+        <v>1051</v>
+      </c>
+      <c r="B86" t="s">
+        <v>100</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0.35</v>
+      </c>
+      <c r="F86">
+        <v>1.2</v>
+      </c>
+      <c r="G86">
+        <v>60</v>
+      </c>
+      <c r="H86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87">
+        <v>1052</v>
+      </c>
+      <c r="B87" t="s">
+        <v>101</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>0.35</v>
+      </c>
+      <c r="F87">
+        <v>1.2</v>
+      </c>
+      <c r="G87">
+        <v>60</v>
+      </c>
+      <c r="H87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88">
+        <v>1061</v>
+      </c>
+      <c r="B88" t="s">
+        <v>102</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0.35</v>
+      </c>
+      <c r="F88">
+        <v>1.2</v>
+      </c>
+      <c r="G88">
+        <v>60</v>
+      </c>
+      <c r="H88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89">
+        <v>1062</v>
+      </c>
+      <c r="B89" t="s">
+        <v>103</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0.35</v>
+      </c>
+      <c r="F89">
+        <v>1.2</v>
+      </c>
+      <c r="G89">
+        <v>60</v>
+      </c>
+      <c r="H89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90">
+        <v>1071</v>
+      </c>
+      <c r="B90" t="s">
+        <v>104</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0.35</v>
+      </c>
+      <c r="F90">
+        <v>1.2</v>
+      </c>
+      <c r="G90">
+        <v>60</v>
+      </c>
+      <c r="H90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91">
+        <v>1081</v>
+      </c>
+      <c r="B91" t="s">
+        <v>105</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0.35</v>
+      </c>
+      <c r="F91">
+        <v>1.2</v>
+      </c>
+      <c r="G91">
+        <v>60</v>
+      </c>
+      <c r="H91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92">
+        <v>1091</v>
+      </c>
+      <c r="B92" t="s">
+        <v>106</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>0.35</v>
+      </c>
+      <c r="F92">
+        <v>1.2</v>
+      </c>
+      <c r="G92">
+        <v>60</v>
+      </c>
+      <c r="H92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93">
+        <v>1092</v>
+      </c>
+      <c r="B93" t="s">
+        <v>107</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>0.35</v>
+      </c>
+      <c r="F93">
+        <v>1.2</v>
+      </c>
+      <c r="G93">
+        <v>60</v>
+      </c>
+      <c r="H93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94">
+        <v>1101</v>
+      </c>
+      <c r="B94" t="s">
+        <v>108</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>0.5</v>
+      </c>
+      <c r="F94">
+        <v>1.2</v>
+      </c>
+      <c r="G94">
+        <v>60</v>
+      </c>
+      <c r="H94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95">
+        <v>1102</v>
+      </c>
+      <c r="B95" t="s">
+        <v>109</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>0.5</v>
+      </c>
+      <c r="F95">
+        <v>1.2</v>
+      </c>
+      <c r="G95">
+        <v>60</v>
+      </c>
+      <c r="H95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96">
+        <v>1103</v>
+      </c>
+      <c r="B96" t="s">
+        <v>110</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>0.5</v>
+      </c>
+      <c r="F96">
+        <v>1.2</v>
+      </c>
+      <c r="G96">
+        <v>60</v>
+      </c>
+      <c r="H96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97">
+        <v>1104</v>
+      </c>
+      <c r="B97" t="s">
+        <v>111</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>0.5</v>
+      </c>
+      <c r="F97">
+        <v>1.2</v>
+      </c>
+      <c r="G97">
+        <v>60</v>
+      </c>
+      <c r="H97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98">
+        <v>1105</v>
+      </c>
+      <c r="B98" t="s">
+        <v>112</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>0.5</v>
+      </c>
+      <c r="F98">
+        <v>1.2</v>
+      </c>
+      <c r="G98">
+        <v>60</v>
+      </c>
+      <c r="H98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99">
+        <v>1106</v>
+      </c>
+      <c r="B99" t="s">
+        <v>113</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>0.5</v>
+      </c>
+      <c r="F99">
+        <v>1.2</v>
+      </c>
+      <c r="G99">
+        <v>60</v>
+      </c>
+      <c r="H99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100">
+        <v>1107</v>
+      </c>
+      <c r="B100" t="s">
+        <v>114</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>0.5</v>
+      </c>
+      <c r="F100">
+        <v>1.2</v>
+      </c>
+      <c r="G100">
+        <v>60</v>
+      </c>
+      <c r="H100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101">
+        <v>1108</v>
+      </c>
+      <c r="B101" t="s">
+        <v>115</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>0.5</v>
+      </c>
+      <c r="F101">
+        <v>1.2</v>
+      </c>
+      <c r="G101">
+        <v>60</v>
+      </c>
+      <c r="H101" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102">
+        <v>1109</v>
+      </c>
+      <c r="B102" t="s">
+        <v>116</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <v>0.5</v>
+      </c>
+      <c r="F102">
+        <v>1.2</v>
+      </c>
+      <c r="G102">
+        <v>60</v>
+      </c>
+      <c r="H102" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103">
+        <v>1201</v>
+      </c>
+      <c r="B103" t="s">
+        <v>117</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>0.5</v>
+      </c>
+      <c r="F103">
+        <v>1.2</v>
+      </c>
+      <c r="G103">
+        <v>60</v>
+      </c>
+      <c r="H103" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104">
+        <v>1202</v>
+      </c>
+      <c r="B104" t="s">
+        <v>118</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>0.5</v>
+      </c>
+      <c r="F104">
+        <v>1.2</v>
+      </c>
+      <c r="G104">
+        <v>60</v>
+      </c>
+      <c r="H104" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105">
+        <v>1211</v>
+      </c>
+      <c r="B105" t="s">
+        <v>119</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>0.5</v>
+      </c>
+      <c r="F105">
+        <v>1.2</v>
+      </c>
+      <c r="G105">
+        <v>60</v>
+      </c>
+      <c r="H105" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106">
+        <v>1212</v>
+      </c>
+      <c r="B106" t="s">
+        <v>120</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>0.5</v>
+      </c>
+      <c r="F106">
+        <v>1.2</v>
+      </c>
+      <c r="G106">
+        <v>60</v>
+      </c>
+      <c r="H106" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107">
+        <v>1213</v>
+      </c>
+      <c r="B107" t="s">
+        <v>121</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>0.5</v>
+      </c>
+      <c r="F107">
+        <v>1.2</v>
+      </c>
+      <c r="G107">
+        <v>60</v>
+      </c>
+      <c r="H107" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108">
+        <v>1301</v>
+      </c>
+      <c r="B108" t="s">
+        <v>122</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>0.5</v>
+      </c>
+      <c r="F108">
+        <v>1.2</v>
+      </c>
+      <c r="G108">
+        <v>60</v>
+      </c>
+      <c r="H108" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109">
+        <v>1302</v>
+      </c>
+      <c r="B109" t="s">
+        <v>123</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="E109">
+        <v>0.5</v>
+      </c>
+      <c r="F109">
+        <v>1.2</v>
+      </c>
+      <c r="G109">
+        <v>60</v>
+      </c>
+      <c r="H109" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110">
+        <v>1311</v>
+      </c>
+      <c r="B110" t="s">
+        <v>124</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>0.5</v>
+      </c>
+      <c r="F110">
+        <v>1.2</v>
+      </c>
+      <c r="G110">
+        <v>60</v>
+      </c>
+      <c r="H110" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111">
+        <v>1312</v>
+      </c>
+      <c r="B111" t="s">
+        <v>125</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>0.5</v>
+      </c>
+      <c r="F111">
+        <v>1.2</v>
+      </c>
+      <c r="G111">
+        <v>60</v>
+      </c>
+      <c r="H111" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112">
+        <v>1313</v>
+      </c>
+      <c r="B112" t="s">
+        <v>126</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>0.5</v>
+      </c>
+      <c r="F112">
+        <v>1.2</v>
+      </c>
+      <c r="G112">
+        <v>60</v>
+      </c>
+      <c r="H112" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113">
+        <v>1401</v>
+      </c>
+      <c r="B113" t="s">
+        <v>127</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>0.5</v>
+      </c>
+      <c r="F113">
+        <v>1.2</v>
+      </c>
+      <c r="G113">
+        <v>60</v>
+      </c>
+      <c r="H113" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114">
+        <v>1402</v>
+      </c>
+      <c r="B114" t="s">
+        <v>128</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>0.5</v>
+      </c>
+      <c r="F114">
+        <v>1.2</v>
+      </c>
+      <c r="G114">
+        <v>60</v>
+      </c>
+      <c r="H114" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115">
+        <v>1411</v>
+      </c>
+      <c r="B115" t="s">
+        <v>129</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>0.5</v>
+      </c>
+      <c r="F115">
+        <v>1.2</v>
+      </c>
+      <c r="G115">
+        <v>60</v>
+      </c>
+      <c r="H115" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116">
+        <v>1412</v>
+      </c>
+      <c r="B116" t="s">
+        <v>130</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>0.5</v>
+      </c>
+      <c r="F116">
+        <v>1.2</v>
+      </c>
+      <c r="G116">
+        <v>60</v>
+      </c>
+      <c r="H116" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117">
+        <v>1413</v>
+      </c>
+      <c r="B117" t="s">
+        <v>131</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>0.5</v>
+      </c>
+      <c r="F117">
+        <v>1.2</v>
+      </c>
+      <c r="G117">
+        <v>60</v>
+      </c>
+      <c r="H117" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118">
+        <v>2001</v>
+      </c>
+      <c r="B118" t="s">
+        <v>132</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>1</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+      <c r="G118">
+        <v>42</v>
+      </c>
+      <c r="H118" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119">
+        <v>2002</v>
+      </c>
+      <c r="B119" t="s">
+        <v>133</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>1</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+      <c r="G119">
+        <v>42</v>
+      </c>
+      <c r="H119" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120">
+        <v>2003</v>
+      </c>
+      <c r="B120" t="s">
+        <v>134</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>1</v>
+      </c>
+      <c r="F120">
+        <v>1</v>
+      </c>
+      <c r="G120">
+        <v>42</v>
+      </c>
+      <c r="H120" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121">
+        <v>2004</v>
+      </c>
+      <c r="B121" t="s">
+        <v>135</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <v>1</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+      <c r="G121">
+        <v>42</v>
+      </c>
+      <c r="H121" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122">
+        <v>2005</v>
+      </c>
+      <c r="B122" t="s">
+        <v>136</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <v>1</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="G122">
+        <v>42</v>
+      </c>
+      <c r="H122" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123">
+        <v>2006</v>
+      </c>
+      <c r="B123" t="s">
+        <v>137</v>
+      </c>
+      <c r="C123">
+        <v>0</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123">
+        <v>1</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="G123">
+        <v>42</v>
+      </c>
+      <c r="H123" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124">
+        <v>5001</v>
+      </c>
+      <c r="B124" t="s">
+        <v>138</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>1</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+      <c r="G124">
+        <v>42</v>
+      </c>
+      <c r="H124" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125">
+        <v>5002</v>
+      </c>
+      <c r="B125" t="s">
+        <v>139</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="E125">
+        <v>1</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+      <c r="G125">
+        <v>42</v>
+      </c>
+      <c r="H125" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126">
+        <v>5003</v>
+      </c>
+      <c r="B126" t="s">
+        <v>140</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="E126">
+        <v>1</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="G126">
+        <v>42</v>
+      </c>
+      <c r="H126" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127">
+        <v>5004</v>
+      </c>
+      <c r="B127" t="s">
+        <v>141</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <v>1</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="G127">
+        <v>42</v>
+      </c>
+      <c r="H127" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128">
+        <v>5005</v>
+      </c>
+      <c r="B128" t="s">
+        <v>142</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="E128">
+        <v>1</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128">
+        <v>42</v>
+      </c>
+      <c r="H128" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129">
+        <v>5006</v>
+      </c>
+      <c r="B129" t="s">
+        <v>143</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+      <c r="E129">
+        <v>1</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+      <c r="G129">
+        <v>42</v>
+      </c>
+      <c r="H129" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130">
+        <v>5007</v>
+      </c>
+      <c r="B130" t="s">
+        <v>144</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+      <c r="E130">
+        <v>1</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+      <c r="G130">
+        <v>42</v>
+      </c>
+      <c r="H130" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131">
+        <v>5008</v>
+      </c>
+      <c r="B131" t="s">
+        <v>145</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="E131">
+        <v>1</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="G131">
+        <v>42</v>
+      </c>
+      <c r="H131" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132">
         <v>5009</v>
       </c>
-      <c r="B83" t="s">
-        <v>90</v>
-      </c>
-      <c r="C83">
-        <v>0</v>
-      </c>
-      <c r="D83">
-        <v>0</v>
-      </c>
-      <c r="E83">
-        <v>1</v>
-      </c>
-      <c r="F83">
-        <v>1</v>
-      </c>
-      <c r="G83">
+      <c r="B132" t="s">
+        <v>146</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="E132">
+        <v>1</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+      <c r="G132">
         <v>42</v>
       </c>
-      <c r="H83" t="b">
+      <c r="H132" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/Animations.xlsx
+++ b/Assets/Data/Animations.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="332">
   <si>
     <t>Id</t>
   </si>
@@ -70,391 +70,946 @@
     <t>FireOne1</t>
   </si>
   <si>
-    <t>炎攻撃</t>
+    <t>炎攻撃単体1</t>
   </si>
   <si>
     <t>FireOne2</t>
   </si>
   <si>
+    <t>炎攻撃単体2</t>
+  </si>
+  <si>
     <t>FireAll1</t>
   </si>
   <si>
+    <t>炎攻撃全体1</t>
+  </si>
+  <si>
     <t>FireAll2</t>
   </si>
   <si>
+    <t>炎攻撃全体2</t>
+  </si>
+  <si>
     <t>FireAll3</t>
   </si>
   <si>
+    <t>炎攻撃全体3</t>
+  </si>
+  <si>
     <t>ThunderOne1</t>
   </si>
   <si>
-    <t>雷攻撃</t>
+    <t>雷攻撃単体1</t>
   </si>
   <si>
     <t>ThunderOne2</t>
   </si>
   <si>
+    <t>雷攻撃単体2</t>
+  </si>
+  <si>
     <t>ThunderAll1</t>
   </si>
   <si>
+    <t>雷攻撃全体1</t>
+  </si>
+  <si>
     <t>ThunderAll2</t>
   </si>
   <si>
+    <t>雷攻撃全体2</t>
+  </si>
+  <si>
     <t>ThunderAll3</t>
   </si>
   <si>
+    <t>雷攻撃全体3</t>
+  </si>
+  <si>
     <t>IceOne1</t>
   </si>
   <si>
-    <t>氷攻撃</t>
+    <t>氷攻撃単体1</t>
   </si>
   <si>
     <t>IceOne2</t>
   </si>
   <si>
+    <t>氷攻撃単体2</t>
+  </si>
+  <si>
     <t>IceAll1</t>
   </si>
   <si>
+    <t>氷攻撃全体1</t>
+  </si>
+  <si>
     <t>IceAll2</t>
   </si>
   <si>
+    <t>氷攻撃全体2</t>
+  </si>
+  <si>
     <t>IceAll3</t>
   </si>
   <si>
+    <t>氷攻撃全体3</t>
+  </si>
+  <si>
     <t>LightOne1</t>
   </si>
   <si>
-    <t>光攻撃</t>
+    <t>光攻撃単体1</t>
   </si>
   <si>
     <t>LightOne2</t>
   </si>
   <si>
+    <t>光攻撃単体2</t>
+  </si>
+  <si>
     <t>LightAll1</t>
   </si>
   <si>
+    <t>光攻撃全体1</t>
+  </si>
+  <si>
     <t>LightAll2</t>
   </si>
   <si>
+    <t>光攻撃全体2</t>
+  </si>
+  <si>
     <t>LightAll3</t>
   </si>
   <si>
+    <t>光攻撃全体3</t>
+  </si>
+  <si>
     <t>DarknessOne1</t>
   </si>
   <si>
-    <t>闇攻撃</t>
+    <t>闇攻撃単体1</t>
   </si>
   <si>
     <t>DarknessOne2</t>
   </si>
   <si>
+    <t>闇攻撃単体2</t>
+  </si>
+  <si>
     <t>DarknessAll1</t>
   </si>
   <si>
+    <t>闇攻撃全体1</t>
+  </si>
+  <si>
     <t>DarknessAll2</t>
   </si>
   <si>
+    <t>闇攻撃全体2</t>
+  </si>
+  <si>
     <t>DarknessAll3</t>
   </si>
   <si>
+    <t>闇攻撃全体3</t>
+  </si>
+  <si>
     <t>NeutralOne1</t>
   </si>
   <si>
+    <t>無攻撃単体1</t>
+  </si>
+  <si>
     <t>NeutralOne2</t>
   </si>
   <si>
+    <t>無攻撃単体2</t>
+  </si>
+  <si>
     <t>NeutralAll1</t>
   </si>
   <si>
+    <t>無攻撃全体1</t>
+  </si>
+  <si>
     <t>NeutralAll2</t>
   </si>
   <si>
+    <t>無攻撃全体2</t>
+  </si>
+  <si>
     <t>NeutralAll3</t>
   </si>
   <si>
+    <t>無攻撃全体3</t>
+  </si>
+  <si>
     <t>HealOne1</t>
   </si>
   <si>
-    <t>回復</t>
+    <t>回復単体1</t>
   </si>
   <si>
     <t>HealOne2</t>
   </si>
   <si>
+    <t>回復単体2</t>
+  </si>
+  <si>
     <t>HealAll1</t>
   </si>
   <si>
+    <t>回復全体1</t>
+  </si>
+  <si>
     <t>HealAll2</t>
   </si>
   <si>
+    <t>回復全体2</t>
+  </si>
+  <si>
     <t>CureOne1</t>
   </si>
   <si>
+    <t>治癒単体1</t>
+  </si>
+  <si>
     <t>CureOne2</t>
   </si>
   <si>
+    <t>治癒単体2</t>
+  </si>
+  <si>
     <t>CureAll1</t>
   </si>
   <si>
+    <t>治癒全体1</t>
+  </si>
+  <si>
     <t>CureAll2</t>
   </si>
   <si>
+    <t>治癒全体2</t>
+  </si>
+  <si>
     <t>Revive1</t>
   </si>
   <si>
+    <t>蘇生1</t>
+  </si>
+  <si>
     <t>Revive2</t>
   </si>
   <si>
+    <t>蘇生2</t>
+  </si>
+  <si>
     <t>Powerup1</t>
   </si>
   <si>
+    <t>バフ１</t>
+  </si>
+  <si>
     <t>Powerup2</t>
   </si>
   <si>
+    <t>バフ２</t>
+  </si>
+  <si>
     <t>Powerup3</t>
   </si>
   <si>
+    <t>バフ３</t>
+  </si>
+  <si>
     <t>Powerdown1</t>
   </si>
   <si>
+    <t>デバフ１</t>
+  </si>
+  <si>
     <t>Powerdown2</t>
   </si>
   <si>
+    <t>デバフ２</t>
+  </si>
+  <si>
     <t>Powerdown3</t>
   </si>
   <si>
+    <t>デバフ３</t>
+  </si>
+  <si>
     <t>Bind</t>
   </si>
   <si>
+    <t>拘束</t>
+  </si>
+  <si>
     <t>Absorb</t>
   </si>
   <si>
+    <t>吸収</t>
+  </si>
+  <si>
     <t>Poison</t>
   </si>
   <si>
+    <t>毒</t>
+  </si>
+  <si>
     <t>Blind</t>
   </si>
   <si>
+    <t>暗闇</t>
+  </si>
+  <si>
     <t>Silence</t>
   </si>
   <si>
+    <t>封印</t>
+  </si>
+  <si>
     <t>Sleep</t>
   </si>
   <si>
+    <t>眠り</t>
+  </si>
+  <si>
     <t>Confusion</t>
   </si>
   <si>
+    <t>混乱</t>
+  </si>
+  <si>
     <t>Paralyze</t>
   </si>
   <si>
+    <t>麻痺</t>
+  </si>
+  <si>
     <t>Death</t>
   </si>
   <si>
+    <t>即死</t>
+  </si>
+  <si>
     <t>HitPhysical</t>
   </si>
   <si>
+    <t>物理</t>
+  </si>
+  <si>
     <t>HitEffect</t>
   </si>
   <si>
+    <t>物理エフェクト</t>
+  </si>
+  <si>
     <t>HitFire</t>
   </si>
   <si>
+    <t>物理炎</t>
+  </si>
+  <si>
     <t>HitIce</t>
   </si>
   <si>
+    <t>物理氷</t>
+  </si>
+  <si>
     <t>HitThunder</t>
   </si>
   <si>
+    <t>物理雷</t>
+  </si>
+  <si>
     <t>SlashPhysical</t>
   </si>
   <si>
+    <t>斬撃</t>
+  </si>
+  <si>
     <t>SlashEffect</t>
   </si>
   <si>
+    <t>斬撃エフェクト</t>
+  </si>
+  <si>
     <t>SlashFire</t>
   </si>
   <si>
+    <t>斬撃炎</t>
+  </si>
+  <si>
     <t>SlashIce</t>
   </si>
   <si>
+    <t>斬撃氷</t>
+  </si>
+  <si>
     <t>SlashThunder</t>
   </si>
   <si>
+    <t>斬撃雷</t>
+  </si>
+  <si>
     <t>PiercePhysical</t>
   </si>
   <si>
+    <t>刺突</t>
+  </si>
+  <si>
     <t>PierceEffect</t>
   </si>
   <si>
+    <t>刺突エフェクト</t>
+  </si>
+  <si>
     <t>PierceFire</t>
   </si>
   <si>
+    <t>刺突炎</t>
+  </si>
+  <si>
     <t>PierceIce</t>
   </si>
   <si>
+    <t>刺突氷</t>
+  </si>
+  <si>
     <t>PierceThunder</t>
   </si>
   <si>
+    <t>刺突雷</t>
+  </si>
+  <si>
     <t>ClawPhysical</t>
   </si>
   <si>
+    <t>ひっかき</t>
+  </si>
+  <si>
     <t>ClawEffect</t>
   </si>
   <si>
+    <t>ひっかきエフェクト</t>
+  </si>
+  <si>
     <t>ClawFire</t>
   </si>
   <si>
+    <t>ひっかき炎</t>
+  </si>
+  <si>
     <t>ClawIce</t>
   </si>
   <si>
+    <t>ひっかき氷</t>
+  </si>
+  <si>
     <t>ClawThunder</t>
   </si>
   <si>
+    <t>ひっかき雷</t>
+  </si>
+  <si>
     <t>HitSpecial1</t>
   </si>
   <si>
+    <t>物理必殺１</t>
+  </si>
+  <si>
     <t>HitSpecial2</t>
   </si>
   <si>
+    <t>物理必殺2</t>
+  </si>
+  <si>
     <t>SlashSpecial1</t>
   </si>
   <si>
+    <t>斬撃必殺１</t>
+  </si>
+  <si>
     <t>SlashSpecial2</t>
   </si>
   <si>
+    <t>斬撃必殺2</t>
+  </si>
+  <si>
     <t>PierceSpecial1</t>
   </si>
   <si>
+    <t>刺突必殺１</t>
+  </si>
+  <si>
     <t>PierceSpecial2</t>
   </si>
   <si>
+    <t>刺突必殺2</t>
+  </si>
+  <si>
     <t>ClawSpecial</t>
   </si>
   <si>
+    <t>ひっかき必殺</t>
+  </si>
+  <si>
     <t>ArrowSpecial</t>
   </si>
   <si>
+    <t>弓必殺</t>
+  </si>
+  <si>
     <t>GeneralSpecial1</t>
   </si>
   <si>
+    <t>汎用必殺１</t>
+  </si>
+  <si>
     <t>GeneralSpecial2</t>
   </si>
   <si>
+    <t>汎用必殺２</t>
+  </si>
+  <si>
     <t>Breath</t>
   </si>
   <si>
+    <t>息</t>
+  </si>
+  <si>
     <t>Pollen</t>
   </si>
   <si>
+    <t>胞子</t>
+  </si>
+  <si>
     <t>SonicWave</t>
   </si>
   <si>
+    <t>超音波</t>
+  </si>
+  <si>
     <t>Fog</t>
   </si>
   <si>
+    <t>霧</t>
+  </si>
+  <si>
     <t>Song</t>
   </si>
   <si>
+    <t>歌</t>
+  </si>
+  <si>
     <t>Shout</t>
   </si>
   <si>
+    <t>咆哮</t>
+  </si>
+  <si>
     <t>Sweep</t>
   </si>
   <si>
+    <t>足払い</t>
+  </si>
+  <si>
     <t>Bodyslam</t>
   </si>
   <si>
+    <t>ボディスラム</t>
+  </si>
+  <si>
     <t>Flash</t>
   </si>
   <si>
+    <t>閃光</t>
+  </si>
+  <si>
     <t>WaterOne1</t>
   </si>
   <si>
+    <t>水攻撃単体1</t>
+  </si>
+  <si>
     <t>WaterOne2</t>
   </si>
   <si>
+    <t>水攻撃単体2</t>
+  </si>
+  <si>
     <t>WaterAll1</t>
   </si>
   <si>
+    <t>水攻撃全体1</t>
+  </si>
+  <si>
     <t>WaterAll2</t>
   </si>
   <si>
+    <t>水攻撃全体2</t>
+  </si>
+  <si>
     <t>WaterAll3</t>
   </si>
   <si>
+    <t>水攻撃全体3</t>
+  </si>
+  <si>
     <t>EarthOne1</t>
   </si>
   <si>
+    <t>地攻撃単体1</t>
+  </si>
+  <si>
     <t>EarthOne2</t>
   </si>
   <si>
+    <t>地攻撃単体2</t>
+  </si>
+  <si>
     <t>EarthAll1</t>
   </si>
   <si>
+    <t>地攻撃全体1</t>
+  </si>
+  <si>
     <t>EarthAll2</t>
   </si>
   <si>
+    <t>地攻撃全体2</t>
+  </si>
+  <si>
     <t>EarthAll3</t>
   </si>
   <si>
+    <t>地攻撃全体3</t>
+  </si>
+  <si>
     <t>WindOne1</t>
   </si>
   <si>
+    <t>風攻撃単体1</t>
+  </si>
+  <si>
     <t>WindOne2</t>
   </si>
   <si>
+    <t>風攻撃単体2</t>
+  </si>
+  <si>
     <t>WindAll1</t>
   </si>
   <si>
+    <t>風攻撃全体1</t>
+  </si>
+  <si>
     <t>WindAll2</t>
   </si>
   <si>
+    <t>風攻撃全体2</t>
+  </si>
+  <si>
     <t>WindAll3</t>
   </si>
   <si>
-    <t>NA_Effekseer_Vol_2/NA_v2_3d_Magic Circle_normal</t>
-  </si>
-  <si>
-    <t>NA_Effekseer_Vol_2/NA_v2_3d_Magic Circle_Fire</t>
-  </si>
-  <si>
-    <t>NA_Effekseer_Vol_2/NA_v2_3d_Magic Circle_electric</t>
-  </si>
-  <si>
-    <t>NA_Effekseer_Vol_2/NA_v2_3d_Magic Circle_ice</t>
-  </si>
-  <si>
-    <t>NA_Effekseer_Vol_2/NA_v2_3d_Magic Circle_light</t>
-  </si>
-  <si>
-    <t>NA_Effekseer_Vol_2/NA_v2_3d_Magic Circle_dark</t>
-  </si>
-  <si>
-    <t>MAGICALxSPIRAL/Undine11</t>
-  </si>
-  <si>
-    <t>MAGICALxSPIRAL/Thunder3</t>
-  </si>
-  <si>
-    <t>MAGICALxSPIRAL/Salamander7</t>
-  </si>
-  <si>
-    <t>NA_Effekseer/NA_poison_001</t>
-  </si>
-  <si>
-    <t>MAGICALxSPIRAL/IcicleLocus</t>
-  </si>
-  <si>
-    <t>MAGICALxSPIRAL/Thunder1</t>
-  </si>
-  <si>
-    <t>MAGICALxSPIRAL/AquaPoint</t>
-  </si>
-  <si>
-    <t>MAGICALxSPIRAL/WHead1</t>
-  </si>
-  <si>
-    <t>EffekseerVol_3/NA_v3_3d_electrification_dark</t>
+    <t>風攻撃全体3</t>
+  </si>
+  <si>
+    <t>ファイアボール</t>
+  </si>
+  <si>
+    <t>バーンストーム</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_sword_001</t>
+  </si>
+  <si>
+    <t>ヒートスタンプ</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_magic_006_c1</t>
+  </si>
+  <si>
+    <t>ソードアダプト</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_magic_004_c1</t>
+  </si>
+  <si>
+    <t>インフェルノ</t>
+  </si>
+  <si>
+    <t>NA_Effekseer_Vol_2/NA_v2_2.5d_element reservoir_fire</t>
+  </si>
+  <si>
+    <t>メルトバースト</t>
+  </si>
+  <si>
+    <t>ディスチャージ</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_net_001</t>
+  </si>
+  <si>
+    <t>ライトニングウェブ</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_status_005</t>
+  </si>
+  <si>
+    <t>シャープコード</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_magic_003</t>
+  </si>
+  <si>
+    <t>ショックインパルス</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_exchange_001</t>
+  </si>
+  <si>
+    <t>トラストチェイン</t>
+  </si>
+  <si>
+    <t>tktk01/Blow10</t>
+  </si>
+  <si>
+    <t>ステップリーダー</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_net_002</t>
+  </si>
+  <si>
+    <t>ユビサキデカラメトル</t>
+  </si>
+  <si>
+    <t>EffekseerVol_3/NA_v3_3d_element shot_electric</t>
+  </si>
+  <si>
+    <t>フルバースト</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_aura_003</t>
+  </si>
+  <si>
+    <t>コウソクテンショウ</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_magic_006_c5</t>
+  </si>
+  <si>
+    <t>アクセラレイト</t>
+  </si>
+  <si>
+    <t>NA_Effekseer_Vol_2/NA_v2_2.5d_jump move_normal</t>
+  </si>
+  <si>
+    <t>リフレクセス</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_slash_003_c3</t>
+  </si>
+  <si>
+    <t>アイスブレイド</t>
+  </si>
+  <si>
+    <t>tktk02/Light1</t>
+  </si>
+  <si>
+    <t>カウンターオーラ</t>
+  </si>
+  <si>
+    <t>tktk02/Gun2</t>
+  </si>
+  <si>
+    <t>シールドスペル</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_wave_001</t>
+  </si>
+  <si>
+    <t>エスコートソール</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_magic_006</t>
+  </si>
+  <si>
+    <t>ディープフリーズ</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_barrier_001</t>
+  </si>
+  <si>
+    <t>フリジットシェル</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_magic_008_c3</t>
+  </si>
+  <si>
+    <t>ノロマナカメニナレ</t>
+  </si>
+  <si>
+    <t>EffekseerVol_3/NA_v3_3d_fairy light_1</t>
+  </si>
+  <si>
+    <t>アンチドード</t>
+  </si>
+  <si>
+    <t>EffekseerVol_3/NA_v3_2.5d_fog_2</t>
+  </si>
+  <si>
+    <t>コオリノセカイヘ</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_magic_006_c2</t>
+  </si>
+  <si>
+    <t>バブルブロウ</t>
+  </si>
+  <si>
+    <t>EffekseerVol_3/NA_v3_3d_residue_water</t>
+  </si>
+  <si>
+    <t>アクアミラージュ</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_magic_007</t>
+  </si>
+  <si>
+    <t>セイントレーザー</t>
+  </si>
+  <si>
+    <t>tktk01/Sword7</t>
+  </si>
+  <si>
+    <t>ペネトレイト</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_healing_001</t>
+  </si>
+  <si>
+    <t>ヒーリング</t>
+  </si>
+  <si>
+    <t>tktk01/Light2</t>
+  </si>
+  <si>
+    <t>リフレッシュ</t>
+  </si>
+  <si>
+    <t>tktk02/Light3</t>
+  </si>
+  <si>
+    <t>べネディクション</t>
+  </si>
+  <si>
+    <t>tktk01/Cure2</t>
+  </si>
+  <si>
+    <t>エリクシール</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_aura_005</t>
+  </si>
+  <si>
+    <t>エンジェルフェザー</t>
+  </si>
+  <si>
+    <t>EffekseerVol_3/NA_v3_2.5d_crash_1</t>
+  </si>
+  <si>
+    <t>ブレークザウォール</t>
+  </si>
+  <si>
+    <t>EffekseerVol_3/NA_v3_2.5d_shining_5</t>
+  </si>
+  <si>
+    <t>トリニティレイ</t>
+  </si>
+  <si>
+    <t>tktk01/Cure1</t>
+  </si>
+  <si>
+    <t>ホーリーグレイス</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_magic_006_c7</t>
+  </si>
+  <si>
+    <t>プリズムリフレクター</t>
+  </si>
+  <si>
+    <t>tktk02/Dark1</t>
+  </si>
+  <si>
+    <t>ダークプリズン</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_wave_003</t>
+  </si>
+  <si>
+    <t>ユーサネイジア</t>
+  </si>
+  <si>
+    <t>tktk01/Dark3</t>
+  </si>
+  <si>
+    <t>ドレインヒール</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_magic_002</t>
+  </si>
+  <si>
+    <t>デリートマジック</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_curse_001</t>
+  </si>
+  <si>
+    <t>ディプラヴィティ</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_smoke_003_c7</t>
+  </si>
+  <si>
+    <t>ディストラクション</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_magic_009</t>
+  </si>
+  <si>
+    <t>カオスペイン</t>
+  </si>
+  <si>
+    <t>MakerEffect/Death</t>
+  </si>
+  <si>
+    <t>セメタリーコール</t>
+  </si>
+  <si>
+    <t>MakerEffect/Darkness1</t>
+  </si>
+  <si>
+    <t>セルフカット</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_magic_006_c8</t>
+  </si>
+  <si>
+    <t>ダークネス</t>
+  </si>
+  <si>
+    <t>NA_Effekseer/NA_smoke_004</t>
+  </si>
+  <si>
+    <t>シェイディークラウド</t>
   </si>
 </sst>
 </file>
@@ -462,10 +1017,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -473,14 +1028,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -492,7 +1039,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -505,22 +1060,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -544,14 +1093,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -565,11 +1121,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -583,14 +1139,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -599,7 +1147,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -612,9 +1168,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -629,13 +1184,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -647,13 +1220,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -665,49 +1232,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -725,13 +1274,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,73 +1364,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -820,21 +1375,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -853,6 +1393,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -864,24 +1413,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -905,7 +1436,31 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -928,16 +1483,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -946,127 +1501,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1425,7 +1980,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I132"/>
+  <dimension ref="A1:I167"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="51.1818181818182" customWidth="1"/>
@@ -1678,7 +2233,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>102</v>
       </c>
@@ -1703,13 +2258,16 @@
       <c r="H10" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>111</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1729,13 +2287,16 @@
       <c r="H11" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1755,13 +2316,16 @@
       <c r="H12" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>113</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1780,6 +2344,9 @@
       </c>
       <c r="H13" t="b">
         <v>1</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1787,7 +2354,7 @@
         <v>201</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1808,15 +2375,15 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>202</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1836,13 +2403,16 @@
       <c r="H15" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>211</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1862,13 +2432,16 @@
       <c r="H16" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>212</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1888,13 +2461,16 @@
       <c r="H17" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>213</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1913,6 +2489,9 @@
       </c>
       <c r="H18" t="b">
         <v>1</v>
+      </c>
+      <c r="I18" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1920,7 +2499,7 @@
         <v>301</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1941,15 +2520,15 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20">
         <v>302</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1969,13 +2548,16 @@
       <c r="H20" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21">
         <v>311</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1995,13 +2577,16 @@
       <c r="H21" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="I21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22">
         <v>312</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -2021,13 +2606,16 @@
       <c r="H22" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23">
         <v>313</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2046,6 +2634,9 @@
       </c>
       <c r="H23" t="b">
         <v>1</v>
+      </c>
+      <c r="I23" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -2053,7 +2644,7 @@
         <v>401</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -2074,15 +2665,15 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25">
         <v>402</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -2102,13 +2693,16 @@
       <c r="H25" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="I25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26">
         <v>411</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -2128,13 +2722,16 @@
       <c r="H26" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="I26" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27">
         <v>412</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -2154,13 +2751,16 @@
       <c r="H27" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="I27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28">
         <v>413</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -2179,6 +2779,9 @@
       </c>
       <c r="H28" t="b">
         <v>1</v>
+      </c>
+      <c r="I28" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -2186,7 +2789,7 @@
         <v>501</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -2207,15 +2810,15 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30">
         <v>502</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -2235,13 +2838,16 @@
       <c r="H30" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="I30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31">
         <v>511</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -2261,13 +2867,16 @@
       <c r="H31" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="I31" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32">
         <v>512</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -2287,13 +2896,16 @@
       <c r="H32" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="I32" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33">
         <v>513</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -2313,13 +2925,16 @@
       <c r="H33" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="I33" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34">
         <v>601</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -2339,13 +2954,16 @@
       <c r="H34" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:8">
+      <c r="I34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35">
         <v>602</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -2365,13 +2983,16 @@
       <c r="H35" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="I35" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36">
         <v>611</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2391,13 +3012,16 @@
       <c r="H36" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="I36" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37">
         <v>612</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -2417,13 +3041,16 @@
       <c r="H37" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:8">
+      <c r="I37" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38">
         <v>613</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -2442,6 +3069,9 @@
       </c>
       <c r="H38" t="b">
         <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -2449,7 +3079,7 @@
         <v>701</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -2470,7 +3100,7 @@
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -2478,7 +3108,7 @@
         <v>702</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -2499,7 +3129,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -2507,7 +3137,7 @@
         <v>711</v>
       </c>
       <c r="B41" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2528,7 +3158,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -2536,7 +3166,7 @@
         <v>712</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2557,7 +3187,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -2565,7 +3195,7 @@
         <v>721</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -2586,7 +3216,7 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2594,7 +3224,7 @@
         <v>722</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -2615,7 +3245,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2623,7 +3253,7 @@
         <v>731</v>
       </c>
       <c r="B45" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -2644,7 +3274,7 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2652,7 +3282,7 @@
         <v>732</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -2673,7 +3303,7 @@
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2681,7 +3311,7 @@
         <v>741</v>
       </c>
       <c r="B47" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -2702,7 +3332,7 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2710,7 +3340,7 @@
         <v>742</v>
       </c>
       <c r="B48" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -2731,15 +3361,15 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49">
         <v>801</v>
       </c>
       <c r="B49" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -2759,13 +3389,16 @@
       <c r="H49" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="I49" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50">
         <v>802</v>
       </c>
       <c r="B50" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -2785,13 +3418,16 @@
       <c r="H50" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="I50" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51">
         <v>803</v>
       </c>
       <c r="B51" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -2811,13 +3447,16 @@
       <c r="H51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:8">
+      <c r="I51" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52">
         <v>811</v>
       </c>
       <c r="B52" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -2837,13 +3476,16 @@
       <c r="H52" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:8">
+      <c r="I52" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53">
         <v>812</v>
       </c>
       <c r="B53" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -2863,13 +3505,16 @@
       <c r="H53" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:8">
+      <c r="I53" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54">
         <v>813</v>
       </c>
       <c r="B54" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -2889,13 +3534,16 @@
       <c r="H54" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:8">
+      <c r="I54" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55">
         <v>901</v>
       </c>
       <c r="B55" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -2915,13 +3563,16 @@
       <c r="H55" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:8">
+      <c r="I55" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56">
         <v>902</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -2941,13 +3592,16 @@
       <c r="H56" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:8">
+      <c r="I56" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57">
         <v>903</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -2967,13 +3621,16 @@
       <c r="H57" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:8">
+      <c r="I57" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58">
         <v>904</v>
       </c>
       <c r="B58" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -2993,13 +3650,16 @@
       <c r="H58" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:8">
+      <c r="I58" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59">
         <v>905</v>
       </c>
       <c r="B59" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -3019,13 +3679,16 @@
       <c r="H59" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:8">
+      <c r="I59" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60">
         <v>906</v>
       </c>
       <c r="B60" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -3045,13 +3708,16 @@
       <c r="H60" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:8">
+      <c r="I60" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61">
         <v>907</v>
       </c>
       <c r="B61" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -3071,13 +3737,16 @@
       <c r="H61" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:8">
+      <c r="I61" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62">
         <v>908</v>
       </c>
       <c r="B62" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -3097,13 +3766,16 @@
       <c r="H62" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:8">
+      <c r="I62" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63">
         <v>909</v>
       </c>
       <c r="B63" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -3123,13 +3795,16 @@
       <c r="H63" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:8">
+      <c r="I63" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64">
         <v>1001</v>
       </c>
       <c r="B64" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -3149,13 +3824,16 @@
       <c r="H64" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:8">
+      <c r="I64" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65">
         <v>1002</v>
       </c>
       <c r="B65" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -3175,13 +3853,16 @@
       <c r="H65" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:8">
+      <c r="I65" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66">
         <v>1003</v>
       </c>
       <c r="B66" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3201,13 +3882,16 @@
       <c r="H66" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:8">
+      <c r="I66" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67">
         <v>1004</v>
       </c>
       <c r="B67" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -3227,13 +3911,16 @@
       <c r="H67" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:8">
+      <c r="I67" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68">
         <v>1005</v>
       </c>
       <c r="B68" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -3253,13 +3940,16 @@
       <c r="H68" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:8">
+      <c r="I68" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69">
         <v>1011</v>
       </c>
       <c r="B69" t="s">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -3279,13 +3969,16 @@
       <c r="H69" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:8">
+      <c r="I69" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70">
         <v>1012</v>
       </c>
       <c r="B70" t="s">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -3305,13 +3998,16 @@
       <c r="H70" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:8">
+      <c r="I70" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71">
         <v>1013</v>
       </c>
       <c r="B71" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -3331,13 +4027,16 @@
       <c r="H71" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:8">
+      <c r="I71" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72">
         <v>1014</v>
       </c>
       <c r="B72" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -3357,13 +4056,16 @@
       <c r="H72" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:8">
+      <c r="I72" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
       <c r="A73">
         <v>1015</v>
       </c>
       <c r="B73" t="s">
-        <v>87</v>
+        <v>145</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -3383,13 +4085,16 @@
       <c r="H73" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:8">
+      <c r="I73" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74">
         <v>1021</v>
       </c>
       <c r="B74" t="s">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -3409,13 +4114,16 @@
       <c r="H74" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:8">
+      <c r="I74" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
       <c r="A75">
         <v>1022</v>
       </c>
       <c r="B75" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -3435,13 +4143,16 @@
       <c r="H75" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:8">
+      <c r="I75" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
       <c r="A76">
         <v>1023</v>
       </c>
       <c r="B76" t="s">
-        <v>90</v>
+        <v>151</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3461,13 +4172,16 @@
       <c r="H76" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:8">
+      <c r="I76" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
       <c r="A77">
         <v>1024</v>
       </c>
       <c r="B77" t="s">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -3487,13 +4201,16 @@
       <c r="H77" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:8">
+      <c r="I77" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
       <c r="A78">
         <v>1025</v>
       </c>
       <c r="B78" t="s">
-        <v>92</v>
+        <v>155</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3513,13 +4230,16 @@
       <c r="H78" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:8">
+      <c r="I78" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
       <c r="A79">
         <v>1031</v>
       </c>
       <c r="B79" t="s">
-        <v>93</v>
+        <v>157</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -3539,13 +4259,16 @@
       <c r="H79" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:8">
+      <c r="I79" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
       <c r="A80">
         <v>1032</v>
       </c>
       <c r="B80" t="s">
-        <v>94</v>
+        <v>159</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -3565,13 +4288,16 @@
       <c r="H80" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:8">
+      <c r="I80" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
       <c r="A81">
         <v>1033</v>
       </c>
       <c r="B81" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -3591,13 +4317,16 @@
       <c r="H81" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:8">
+      <c r="I81" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
       <c r="A82">
         <v>1034</v>
       </c>
       <c r="B82" t="s">
-        <v>96</v>
+        <v>163</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -3617,13 +4346,16 @@
       <c r="H82" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:8">
+      <c r="I82" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83">
         <v>1035</v>
       </c>
       <c r="B83" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -3643,13 +4375,16 @@
       <c r="H83" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:8">
+      <c r="I83" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
       <c r="A84">
         <v>1041</v>
       </c>
       <c r="B84" t="s">
-        <v>98</v>
+        <v>167</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -3669,13 +4404,16 @@
       <c r="H84" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:8">
+      <c r="I84" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
       <c r="A85">
         <v>1042</v>
       </c>
       <c r="B85" t="s">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -3695,13 +4433,16 @@
       <c r="H85" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:8">
+      <c r="I85" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
       <c r="A86">
         <v>1051</v>
       </c>
       <c r="B86" t="s">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -3721,13 +4462,16 @@
       <c r="H86" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:8">
+      <c r="I86" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
       <c r="A87">
         <v>1052</v>
       </c>
       <c r="B87" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -3747,13 +4491,16 @@
       <c r="H87" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:8">
+      <c r="I87" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
       <c r="A88">
         <v>1061</v>
       </c>
       <c r="B88" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -3773,13 +4520,16 @@
       <c r="H88" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:8">
+      <c r="I88" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
       <c r="A89">
         <v>1062</v>
       </c>
       <c r="B89" t="s">
-        <v>103</v>
+        <v>177</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -3799,13 +4549,16 @@
       <c r="H89" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:8">
+      <c r="I89" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
       <c r="A90">
         <v>1071</v>
       </c>
       <c r="B90" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -3825,13 +4578,16 @@
       <c r="H90" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:8">
+      <c r="I90" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
       <c r="A91">
         <v>1081</v>
       </c>
       <c r="B91" t="s">
-        <v>105</v>
+        <v>181</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -3851,13 +4607,16 @@
       <c r="H91" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:8">
+      <c r="I91" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
       <c r="A92">
         <v>1091</v>
       </c>
       <c r="B92" t="s">
-        <v>106</v>
+        <v>183</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -3877,13 +4636,16 @@
       <c r="H92" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:8">
+      <c r="I92" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
       <c r="A93">
         <v>1092</v>
       </c>
       <c r="B93" t="s">
-        <v>107</v>
+        <v>185</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -3903,13 +4665,16 @@
       <c r="H93" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:8">
+      <c r="I93" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
       <c r="A94">
         <v>1101</v>
       </c>
       <c r="B94" t="s">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -3929,13 +4694,16 @@
       <c r="H94" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:8">
+      <c r="I94" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
       <c r="A95">
         <v>1102</v>
       </c>
       <c r="B95" t="s">
-        <v>109</v>
+        <v>189</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -3955,13 +4723,16 @@
       <c r="H95" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:8">
+      <c r="I95" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
       <c r="A96">
         <v>1103</v>
       </c>
       <c r="B96" t="s">
-        <v>110</v>
+        <v>191</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -3981,13 +4752,16 @@
       <c r="H96" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:8">
+      <c r="I96" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
       <c r="A97">
         <v>1104</v>
       </c>
       <c r="B97" t="s">
-        <v>111</v>
+        <v>193</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -4007,13 +4781,16 @@
       <c r="H97" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:8">
+      <c r="I97" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
       <c r="A98">
         <v>1105</v>
       </c>
       <c r="B98" t="s">
-        <v>112</v>
+        <v>195</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -4033,13 +4810,16 @@
       <c r="H98" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:8">
+      <c r="I98" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
       <c r="A99">
         <v>1106</v>
       </c>
       <c r="B99" t="s">
-        <v>113</v>
+        <v>197</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -4059,13 +4839,16 @@
       <c r="H99" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:8">
+      <c r="I99" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
       <c r="A100">
         <v>1107</v>
       </c>
       <c r="B100" t="s">
-        <v>114</v>
+        <v>199</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -4085,13 +4868,16 @@
       <c r="H100" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:8">
+      <c r="I100" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
       <c r="A101">
         <v>1108</v>
       </c>
       <c r="B101" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -4111,13 +4897,16 @@
       <c r="H101" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:8">
+      <c r="I101" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
       <c r="A102">
         <v>1109</v>
       </c>
       <c r="B102" t="s">
-        <v>116</v>
+        <v>203</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -4137,13 +4926,16 @@
       <c r="H102" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="1:8">
+      <c r="I102" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
       <c r="A103">
         <v>1201</v>
       </c>
       <c r="B103" t="s">
-        <v>117</v>
+        <v>205</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -4163,13 +4955,16 @@
       <c r="H103" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:8">
+      <c r="I103" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
       <c r="A104">
         <v>1202</v>
       </c>
       <c r="B104" t="s">
-        <v>118</v>
+        <v>207</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -4189,13 +4984,16 @@
       <c r="H104" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:8">
+      <c r="I104" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
       <c r="A105">
         <v>1211</v>
       </c>
       <c r="B105" t="s">
-        <v>119</v>
+        <v>209</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -4215,13 +5013,16 @@
       <c r="H105" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:8">
+      <c r="I105" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
       <c r="A106">
         <v>1212</v>
       </c>
       <c r="B106" t="s">
-        <v>120</v>
+        <v>211</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -4241,13 +5042,16 @@
       <c r="H106" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:8">
+      <c r="I106" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
       <c r="A107">
         <v>1213</v>
       </c>
       <c r="B107" t="s">
-        <v>121</v>
+        <v>213</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -4267,13 +5071,16 @@
       <c r="H107" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:8">
+      <c r="I107" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
       <c r="A108">
         <v>1301</v>
       </c>
       <c r="B108" t="s">
-        <v>122</v>
+        <v>215</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -4293,13 +5100,16 @@
       <c r="H108" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="109" spans="1:8">
+      <c r="I108" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
       <c r="A109">
         <v>1302</v>
       </c>
       <c r="B109" t="s">
-        <v>123</v>
+        <v>217</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -4319,13 +5129,16 @@
       <c r="H109" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:8">
+      <c r="I109" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
       <c r="A110">
         <v>1311</v>
       </c>
       <c r="B110" t="s">
-        <v>124</v>
+        <v>219</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -4345,13 +5158,16 @@
       <c r="H110" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:8">
+      <c r="I110" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
       <c r="A111">
         <v>1312</v>
       </c>
       <c r="B111" t="s">
-        <v>125</v>
+        <v>221</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -4371,13 +5187,16 @@
       <c r="H111" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:8">
+      <c r="I111" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
       <c r="A112">
         <v>1313</v>
       </c>
       <c r="B112" t="s">
-        <v>126</v>
+        <v>223</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -4397,13 +5216,16 @@
       <c r="H112" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:8">
+      <c r="I112" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
       <c r="A113">
         <v>1401</v>
       </c>
       <c r="B113" t="s">
-        <v>127</v>
+        <v>225</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -4423,13 +5245,16 @@
       <c r="H113" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:8">
+      <c r="I113" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
       <c r="A114">
         <v>1402</v>
       </c>
       <c r="B114" t="s">
-        <v>128</v>
+        <v>227</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -4449,13 +5274,16 @@
       <c r="H114" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:8">
+      <c r="I114" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
       <c r="A115">
         <v>1411</v>
       </c>
       <c r="B115" t="s">
-        <v>129</v>
+        <v>229</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -4475,13 +5303,16 @@
       <c r="H115" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:8">
+      <c r="I115" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
       <c r="A116">
         <v>1412</v>
       </c>
       <c r="B116" t="s">
-        <v>130</v>
+        <v>231</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -4501,13 +5332,16 @@
       <c r="H116" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:8">
+      <c r="I116" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
       <c r="A117">
         <v>1413</v>
       </c>
       <c r="B117" t="s">
-        <v>131</v>
+        <v>233</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -4527,13 +5361,16 @@
       <c r="H117" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:8">
+      <c r="I117" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
       <c r="A118">
-        <v>2001</v>
+        <v>2101</v>
       </c>
       <c r="B118" t="s">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -4542,24 +5379,27 @@
         <v>0</v>
       </c>
       <c r="E118">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F118">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G118">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H118" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:8">
+      <c r="I118" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
       <c r="A119">
-        <v>2002</v>
+        <v>2102</v>
       </c>
       <c r="B119" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -4568,24 +5408,27 @@
         <v>0</v>
       </c>
       <c r="E119">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F119">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G119">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H119" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:8">
+      <c r="I119" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
       <c r="A120">
-        <v>2003</v>
+        <v>2103</v>
       </c>
       <c r="B120" t="s">
-        <v>134</v>
+        <v>237</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -4594,24 +5437,27 @@
         <v>0</v>
       </c>
       <c r="E120">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F120">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G120">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H120" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:8">
+      <c r="I120" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
       <c r="A121">
-        <v>2004</v>
+        <v>2104</v>
       </c>
       <c r="B121" t="s">
-        <v>135</v>
+        <v>239</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -4620,24 +5466,27 @@
         <v>0</v>
       </c>
       <c r="E121">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F121">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G121">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H121" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:8">
+      <c r="I121" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
       <c r="A122">
-        <v>2005</v>
+        <v>2105</v>
       </c>
       <c r="B122" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -4646,24 +5495,27 @@
         <v>0</v>
       </c>
       <c r="E122">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F122">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G122">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H122" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:8">
+      <c r="I122" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
       <c r="A123">
-        <v>2006</v>
+        <v>2106</v>
       </c>
       <c r="B123" t="s">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -4672,24 +5524,27 @@
         <v>0</v>
       </c>
       <c r="E123">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F123">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G123">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H123" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="124" spans="1:8">
+      <c r="I123" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
       <c r="A124">
-        <v>5001</v>
+        <v>2201</v>
       </c>
       <c r="B124" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -4698,24 +5553,27 @@
         <v>0</v>
       </c>
       <c r="E124">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F124">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G124">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H124" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:8">
+      <c r="I124" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
       <c r="A125">
-        <v>5002</v>
+        <v>2202</v>
       </c>
       <c r="B125" t="s">
-        <v>139</v>
+        <v>246</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -4724,24 +5582,27 @@
         <v>0</v>
       </c>
       <c r="E125">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F125">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G125">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H125" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="126" spans="1:8">
+      <c r="I125" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
       <c r="A126">
-        <v>5003</v>
+        <v>2203</v>
       </c>
       <c r="B126" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -4750,24 +5611,27 @@
         <v>0</v>
       </c>
       <c r="E126">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F126">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G126">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H126" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="127" spans="1:8">
+      <c r="I126" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
       <c r="A127">
-        <v>5004</v>
+        <v>2204</v>
       </c>
       <c r="B127" t="s">
-        <v>141</v>
+        <v>250</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -4776,24 +5640,27 @@
         <v>0</v>
       </c>
       <c r="E127">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F127">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G127">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H127" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:8">
+      <c r="I127" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
       <c r="A128">
-        <v>5005</v>
+        <v>2205</v>
       </c>
       <c r="B128" t="s">
-        <v>142</v>
+        <v>252</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -4802,24 +5669,27 @@
         <v>0</v>
       </c>
       <c r="E128">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F128">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G128">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H128" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:8">
+      <c r="I128" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
       <c r="A129">
-        <v>5006</v>
+        <v>2206</v>
       </c>
       <c r="B129" t="s">
-        <v>143</v>
+        <v>254</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -4828,24 +5698,27 @@
         <v>0</v>
       </c>
       <c r="E129">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F129">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G129">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H129" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:8">
+      <c r="I129" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
       <c r="A130">
-        <v>5007</v>
+        <v>2207</v>
       </c>
       <c r="B130" t="s">
-        <v>144</v>
+        <v>256</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -4854,24 +5727,27 @@
         <v>0</v>
       </c>
       <c r="E130">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F130">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G130">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H130" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:8">
+      <c r="I130" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
       <c r="A131">
-        <v>5008</v>
+        <v>2208</v>
       </c>
       <c r="B131" t="s">
-        <v>145</v>
+        <v>258</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -4880,24 +5756,27 @@
         <v>0</v>
       </c>
       <c r="E131">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F131">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G131">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H131" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="132" spans="1:8">
+      <c r="I131" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
       <c r="A132">
-        <v>5009</v>
+        <v>2209</v>
       </c>
       <c r="B132" t="s">
-        <v>146</v>
+        <v>260</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -4906,16 +5785,1034 @@
         <v>0</v>
       </c>
       <c r="E132">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F132">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G132">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="H132" t="b">
         <v>1</v>
+      </c>
+      <c r="I132" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133">
+        <v>2210</v>
+      </c>
+      <c r="B133" t="s">
+        <v>262</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <v>0.5</v>
+      </c>
+      <c r="F133">
+        <v>1.2</v>
+      </c>
+      <c r="G133">
+        <v>60</v>
+      </c>
+      <c r="H133" t="b">
+        <v>1</v>
+      </c>
+      <c r="I133" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134">
+        <v>2211</v>
+      </c>
+      <c r="B134" t="s">
+        <v>264</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+      <c r="E134">
+        <v>0.5</v>
+      </c>
+      <c r="F134">
+        <v>1.2</v>
+      </c>
+      <c r="G134">
+        <v>60</v>
+      </c>
+      <c r="H134" t="b">
+        <v>1</v>
+      </c>
+      <c r="I134" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135">
+        <v>2301</v>
+      </c>
+      <c r="B135" t="s">
+        <v>266</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="E135">
+        <v>0.5</v>
+      </c>
+      <c r="F135">
+        <v>1.2</v>
+      </c>
+      <c r="G135">
+        <v>60</v>
+      </c>
+      <c r="H135" t="b">
+        <v>1</v>
+      </c>
+      <c r="I135" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136">
+        <v>2302</v>
+      </c>
+      <c r="B136" t="s">
+        <v>268</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+      <c r="E136">
+        <v>0.5</v>
+      </c>
+      <c r="F136">
+        <v>1.2</v>
+      </c>
+      <c r="G136">
+        <v>60</v>
+      </c>
+      <c r="H136" t="b">
+        <v>1</v>
+      </c>
+      <c r="I136" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
+      <c r="A137">
+        <v>2303</v>
+      </c>
+      <c r="B137" t="s">
+        <v>270</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+      <c r="E137">
+        <v>0.5</v>
+      </c>
+      <c r="F137">
+        <v>1.2</v>
+      </c>
+      <c r="G137">
+        <v>60</v>
+      </c>
+      <c r="H137" t="b">
+        <v>1</v>
+      </c>
+      <c r="I137" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138">
+        <v>2304</v>
+      </c>
+      <c r="B138" t="s">
+        <v>272</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+      <c r="E138">
+        <v>0.5</v>
+      </c>
+      <c r="F138">
+        <v>1.2</v>
+      </c>
+      <c r="G138">
+        <v>60</v>
+      </c>
+      <c r="H138" t="b">
+        <v>1</v>
+      </c>
+      <c r="I138" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139">
+        <v>2305</v>
+      </c>
+      <c r="B139" t="s">
+        <v>274</v>
+      </c>
+      <c r="C139">
+        <v>0</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+      <c r="E139">
+        <v>0.5</v>
+      </c>
+      <c r="F139">
+        <v>1.2</v>
+      </c>
+      <c r="G139">
+        <v>60</v>
+      </c>
+      <c r="H139" t="b">
+        <v>1</v>
+      </c>
+      <c r="I139" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
+      <c r="A140">
+        <v>2306</v>
+      </c>
+      <c r="B140" t="s">
+        <v>276</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+      <c r="E140">
+        <v>0.5</v>
+      </c>
+      <c r="F140">
+        <v>1.2</v>
+      </c>
+      <c r="G140">
+        <v>60</v>
+      </c>
+      <c r="H140" t="b">
+        <v>1</v>
+      </c>
+      <c r="I140" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141">
+        <v>2307</v>
+      </c>
+      <c r="B141" t="s">
+        <v>278</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+      <c r="E141">
+        <v>0.5</v>
+      </c>
+      <c r="F141">
+        <v>1.2</v>
+      </c>
+      <c r="G141">
+        <v>60</v>
+      </c>
+      <c r="H141" t="b">
+        <v>1</v>
+      </c>
+      <c r="I141" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="A142">
+        <v>2308</v>
+      </c>
+      <c r="B142" t="s">
+        <v>280</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="E142">
+        <v>0.5</v>
+      </c>
+      <c r="F142">
+        <v>1.2</v>
+      </c>
+      <c r="G142">
+        <v>60</v>
+      </c>
+      <c r="H142" t="b">
+        <v>1</v>
+      </c>
+      <c r="I142" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="A143">
+        <v>2309</v>
+      </c>
+      <c r="B143" t="s">
+        <v>282</v>
+      </c>
+      <c r="C143">
+        <v>0</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+      <c r="E143">
+        <v>0.5</v>
+      </c>
+      <c r="F143">
+        <v>1.2</v>
+      </c>
+      <c r="G143">
+        <v>60</v>
+      </c>
+      <c r="H143" t="b">
+        <v>1</v>
+      </c>
+      <c r="I143" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
+      <c r="A144">
+        <v>2310</v>
+      </c>
+      <c r="B144" t="s">
+        <v>284</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+      <c r="E144">
+        <v>0.5</v>
+      </c>
+      <c r="F144">
+        <v>1.2</v>
+      </c>
+      <c r="G144">
+        <v>60</v>
+      </c>
+      <c r="H144" t="b">
+        <v>1</v>
+      </c>
+      <c r="I144" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
+      <c r="A145">
+        <v>2311</v>
+      </c>
+      <c r="B145" t="s">
+        <v>286</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+      <c r="E145">
+        <v>0.5</v>
+      </c>
+      <c r="F145">
+        <v>1.2</v>
+      </c>
+      <c r="G145">
+        <v>60</v>
+      </c>
+      <c r="H145" t="b">
+        <v>1</v>
+      </c>
+      <c r="I145" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="A146">
+        <v>2401</v>
+      </c>
+      <c r="B146" t="s">
+        <v>288</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+      <c r="E146">
+        <v>0.5</v>
+      </c>
+      <c r="F146">
+        <v>1.2</v>
+      </c>
+      <c r="G146">
+        <v>60</v>
+      </c>
+      <c r="H146" t="b">
+        <v>1</v>
+      </c>
+      <c r="I146" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
+      <c r="A147">
+        <v>2402</v>
+      </c>
+      <c r="B147" t="s">
+        <v>290</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+      <c r="E147">
+        <v>0.5</v>
+      </c>
+      <c r="F147">
+        <v>1.2</v>
+      </c>
+      <c r="G147">
+        <v>60</v>
+      </c>
+      <c r="H147" t="b">
+        <v>1</v>
+      </c>
+      <c r="I147" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148">
+        <v>2403</v>
+      </c>
+      <c r="B148" t="s">
+        <v>292</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+      <c r="D148">
+        <v>0</v>
+      </c>
+      <c r="E148">
+        <v>0.5</v>
+      </c>
+      <c r="F148">
+        <v>1.2</v>
+      </c>
+      <c r="G148">
+        <v>60</v>
+      </c>
+      <c r="H148" t="b">
+        <v>1</v>
+      </c>
+      <c r="I148" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149">
+        <v>2404</v>
+      </c>
+      <c r="B149" t="s">
+        <v>294</v>
+      </c>
+      <c r="C149">
+        <v>0</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+      <c r="E149">
+        <v>0.5</v>
+      </c>
+      <c r="F149">
+        <v>1.2</v>
+      </c>
+      <c r="G149">
+        <v>60</v>
+      </c>
+      <c r="H149" t="b">
+        <v>1</v>
+      </c>
+      <c r="I149" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150">
+        <v>2405</v>
+      </c>
+      <c r="B150" t="s">
+        <v>296</v>
+      </c>
+      <c r="C150">
+        <v>0</v>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+      <c r="E150">
+        <v>0.5</v>
+      </c>
+      <c r="F150">
+        <v>1.2</v>
+      </c>
+      <c r="G150">
+        <v>60</v>
+      </c>
+      <c r="H150" t="b">
+        <v>1</v>
+      </c>
+      <c r="I150" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151">
+        <v>2406</v>
+      </c>
+      <c r="B151" t="s">
+        <v>298</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
+      <c r="D151">
+        <v>0</v>
+      </c>
+      <c r="E151">
+        <v>0.5</v>
+      </c>
+      <c r="F151">
+        <v>1.2</v>
+      </c>
+      <c r="G151">
+        <v>60</v>
+      </c>
+      <c r="H151" t="b">
+        <v>1</v>
+      </c>
+      <c r="I151" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="A152">
+        <v>2407</v>
+      </c>
+      <c r="B152" t="s">
+        <v>300</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+      <c r="D152">
+        <v>0</v>
+      </c>
+      <c r="E152">
+        <v>0.5</v>
+      </c>
+      <c r="F152">
+        <v>1.2</v>
+      </c>
+      <c r="G152">
+        <v>60</v>
+      </c>
+      <c r="H152" t="b">
+        <v>1</v>
+      </c>
+      <c r="I152" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
+      <c r="A153">
+        <v>2408</v>
+      </c>
+      <c r="B153" t="s">
+        <v>302</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+      <c r="E153">
+        <v>0.5</v>
+      </c>
+      <c r="F153">
+        <v>1.2</v>
+      </c>
+      <c r="G153">
+        <v>60</v>
+      </c>
+      <c r="H153" t="b">
+        <v>1</v>
+      </c>
+      <c r="I153" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154">
+        <v>2409</v>
+      </c>
+      <c r="B154" t="s">
+        <v>304</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+      <c r="D154">
+        <v>0</v>
+      </c>
+      <c r="E154">
+        <v>0.5</v>
+      </c>
+      <c r="F154">
+        <v>1.2</v>
+      </c>
+      <c r="G154">
+        <v>60</v>
+      </c>
+      <c r="H154" t="b">
+        <v>1</v>
+      </c>
+      <c r="I154" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155">
+        <v>2410</v>
+      </c>
+      <c r="B155" t="s">
+        <v>306</v>
+      </c>
+      <c r="C155">
+        <v>0</v>
+      </c>
+      <c r="D155">
+        <v>0</v>
+      </c>
+      <c r="E155">
+        <v>0.5</v>
+      </c>
+      <c r="F155">
+        <v>1.2</v>
+      </c>
+      <c r="G155">
+        <v>60</v>
+      </c>
+      <c r="H155" t="b">
+        <v>1</v>
+      </c>
+      <c r="I155" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
+      <c r="A156">
+        <v>2411</v>
+      </c>
+      <c r="B156" t="s">
+        <v>308</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+      <c r="D156">
+        <v>0</v>
+      </c>
+      <c r="E156">
+        <v>0.5</v>
+      </c>
+      <c r="F156">
+        <v>1.2</v>
+      </c>
+      <c r="G156">
+        <v>60</v>
+      </c>
+      <c r="H156" t="b">
+        <v>1</v>
+      </c>
+      <c r="I156" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
+      <c r="A157">
+        <v>2501</v>
+      </c>
+      <c r="B157" t="s">
+        <v>310</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
+      </c>
+      <c r="D157">
+        <v>0</v>
+      </c>
+      <c r="E157">
+        <v>0.5</v>
+      </c>
+      <c r="F157">
+        <v>1.2</v>
+      </c>
+      <c r="G157">
+        <v>60</v>
+      </c>
+      <c r="H157" t="b">
+        <v>1</v>
+      </c>
+      <c r="I157" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
+      <c r="A158">
+        <v>2502</v>
+      </c>
+      <c r="B158" t="s">
+        <v>312</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
+      <c r="D158">
+        <v>0</v>
+      </c>
+      <c r="E158">
+        <v>0.5</v>
+      </c>
+      <c r="F158">
+        <v>1.2</v>
+      </c>
+      <c r="G158">
+        <v>60</v>
+      </c>
+      <c r="H158" t="b">
+        <v>1</v>
+      </c>
+      <c r="I158" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
+      <c r="A159">
+        <v>2503</v>
+      </c>
+      <c r="B159" t="s">
+        <v>314</v>
+      </c>
+      <c r="C159">
+        <v>0</v>
+      </c>
+      <c r="D159">
+        <v>0</v>
+      </c>
+      <c r="E159">
+        <v>0.5</v>
+      </c>
+      <c r="F159">
+        <v>1.2</v>
+      </c>
+      <c r="G159">
+        <v>60</v>
+      </c>
+      <c r="H159" t="b">
+        <v>1</v>
+      </c>
+      <c r="I159" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
+      <c r="A160">
+        <v>2504</v>
+      </c>
+      <c r="B160" t="s">
+        <v>316</v>
+      </c>
+      <c r="C160">
+        <v>0</v>
+      </c>
+      <c r="D160">
+        <v>0</v>
+      </c>
+      <c r="E160">
+        <v>0.5</v>
+      </c>
+      <c r="F160">
+        <v>1.2</v>
+      </c>
+      <c r="G160">
+        <v>60</v>
+      </c>
+      <c r="H160" t="b">
+        <v>1</v>
+      </c>
+      <c r="I160" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
+      <c r="A161">
+        <v>2505</v>
+      </c>
+      <c r="B161" t="s">
+        <v>318</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+      <c r="D161">
+        <v>0</v>
+      </c>
+      <c r="E161">
+        <v>0.5</v>
+      </c>
+      <c r="F161">
+        <v>1.2</v>
+      </c>
+      <c r="G161">
+        <v>60</v>
+      </c>
+      <c r="H161" t="b">
+        <v>1</v>
+      </c>
+      <c r="I161" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
+      <c r="A162">
+        <v>2506</v>
+      </c>
+      <c r="B162" t="s">
+        <v>320</v>
+      </c>
+      <c r="C162">
+        <v>0</v>
+      </c>
+      <c r="D162">
+        <v>0</v>
+      </c>
+      <c r="E162">
+        <v>0.5</v>
+      </c>
+      <c r="F162">
+        <v>1.2</v>
+      </c>
+      <c r="G162">
+        <v>60</v>
+      </c>
+      <c r="H162" t="b">
+        <v>1</v>
+      </c>
+      <c r="I162" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
+      <c r="A163">
+        <v>2507</v>
+      </c>
+      <c r="B163" t="s">
+        <v>322</v>
+      </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+      <c r="E163">
+        <v>0.5</v>
+      </c>
+      <c r="F163">
+        <v>1.2</v>
+      </c>
+      <c r="G163">
+        <v>60</v>
+      </c>
+      <c r="H163" t="b">
+        <v>1</v>
+      </c>
+      <c r="I163" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="A164">
+        <v>2508</v>
+      </c>
+      <c r="B164" t="s">
+        <v>324</v>
+      </c>
+      <c r="C164">
+        <v>0</v>
+      </c>
+      <c r="D164">
+        <v>0</v>
+      </c>
+      <c r="E164">
+        <v>0.5</v>
+      </c>
+      <c r="F164">
+        <v>1.2</v>
+      </c>
+      <c r="G164">
+        <v>60</v>
+      </c>
+      <c r="H164" t="b">
+        <v>1</v>
+      </c>
+      <c r="I164" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
+      <c r="A165">
+        <v>2509</v>
+      </c>
+      <c r="B165" t="s">
+        <v>326</v>
+      </c>
+      <c r="C165">
+        <v>0</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+      <c r="E165">
+        <v>0.5</v>
+      </c>
+      <c r="F165">
+        <v>1.2</v>
+      </c>
+      <c r="G165">
+        <v>60</v>
+      </c>
+      <c r="H165" t="b">
+        <v>1</v>
+      </c>
+      <c r="I165" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
+      <c r="A166">
+        <v>2510</v>
+      </c>
+      <c r="B166" t="s">
+        <v>328</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+      <c r="D166">
+        <v>0</v>
+      </c>
+      <c r="E166">
+        <v>0.5</v>
+      </c>
+      <c r="F166">
+        <v>1.2</v>
+      </c>
+      <c r="G166">
+        <v>60</v>
+      </c>
+      <c r="H166" t="b">
+        <v>1</v>
+      </c>
+      <c r="I166" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
+      <c r="A167">
+        <v>2511</v>
+      </c>
+      <c r="B167" t="s">
+        <v>330</v>
+      </c>
+      <c r="C167">
+        <v>0</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="E167">
+        <v>0.5</v>
+      </c>
+      <c r="F167">
+        <v>1.2</v>
+      </c>
+      <c r="G167">
+        <v>60</v>
+      </c>
+      <c r="H167" t="b">
+        <v>1</v>
+      </c>
+      <c r="I167" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>
